--- a/artfynd/S 4464-2023 artfynd.xlsx
+++ b/artfynd/S 4464-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4628544</v>
+        <v>136954306</v>
       </c>
       <c r="B4" t="n">
-        <v>99781</v>
+        <v>43471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,37 +945,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222309</v>
+        <v>101298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Sotnätfjäril</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Melitaea diamina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>(Lang, 1789)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Heden, ost-sydost bystugan, Dlr</t>
+          <t>Lissheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499913</v>
+        <v>500039</v>
       </c>
       <c r="R4" t="n">
-        <v>6729284</v>
+        <v>6729384</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,17 +999,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-06-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-06-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>enstaka exemplar finns även här och där på åsarna österut.</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,83 +1015,73 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Bryn mot sandig brukningsvägskant</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Pär Dahlström</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pär Dahlström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4628544</t>
+          <t>https://artportalen.se/Sighting/136954306</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>497103</v>
+        <v>4628544</v>
       </c>
       <c r="B5" t="n">
-        <v>101345</v>
+        <v>99781</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1853</v>
+        <v>222309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Heden (W-Lek-0028), Dlr</t>
+          <t>Heden, ost-sydost bystugan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500208</v>
+        <v>499913</v>
       </c>
       <c r="R5" t="n">
-        <v>6729002</v>
+        <v>6729284</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,24 +1103,19 @@
           <t>Leksand</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>W-Lek-0028</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2012-06-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2003-12-31</t>
+          <t>2012-06-25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>spritt bestånd på åssluttning (Frasse Blomberg)</t>
+          <t>enstaka exemplar finns även här och där på åsarna österut.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,34 +1129,30 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>åssluttning</t>
+          <t>Bryn mot sandig brukningsvägskant</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Dalarna Floraväktarna</t>
+          <t>Pär Dahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Dalarna Floraväktarna</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Pär Dahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/497103</t>
+          <t>https://artportalen.se/Sighting/4628544</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>525892</v>
+        <v>497103</v>
       </c>
       <c r="B6" t="n">
         <v>101345</v>
@@ -1206,7 +1182,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1214,21 +1190,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Heden  Leksand f:s, Dlr</t>
+          <t>Heden (W-Lek-0028), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500288</v>
+        <v>500208</v>
       </c>
       <c r="R6" t="n">
-        <v>6729025</v>
+        <v>6729002</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,19 +1224,24 @@
           <t>Leksand</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>W-Lek-0028</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-06-25</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-06-25</t>
+          <t>2003-12-31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ej med i Frasse Blombergs inventering från 2003. 7 täta plantor utan blomma. Blommade med 4 stänglar i fjol. Märkt med en pinne mosippa. 70m ost nordost( W-Lek-0028)</t>
+          <t>spritt bestånd på åssluttning (Frasse Blomberg)</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,24 +1261,28 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Pär Dahlström</t>
+          <t>Dalarna Floraväktarna</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pär Dahlström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Dalarna Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/525892</t>
+          <t>https://artportalen.se/Sighting/497103</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6820542</v>
+        <v>525892</v>
       </c>
       <c r="B7" t="n">
         <v>101345</v>
@@ -1332,7 +1312,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1340,18 +1320,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väst Storhedens skjutbana, Dlr</t>
+          <t>Heden  Leksand f:s, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500319</v>
+        <v>500288</v>
       </c>
       <c r="R7" t="n">
-        <v>6729052</v>
+        <v>6729025</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1378,17 +1361,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2013-06-24</t>
+          <t>2012-06-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2013-06-24</t>
+          <t>2012-06-25</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I och på kanten av körväg. Sterila. Visades av förbipasserande med hund.</t>
+          <t>Ej med i Frasse Blombergs inventering från 2003. 7 täta plantor utan blomma. Blommade med 4 stänglar i fjol. Märkt med en pinne mosippa. 70m ost nordost( W-Lek-0028)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,7 +1385,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>I och i kant av sandig körväg</t>
+          <t>åssluttning</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1419,13 +1402,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6820542</t>
+          <t>https://artportalen.se/Sighting/525892</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>84768990</v>
+        <v>6820542</v>
       </c>
       <c r="B8" t="n">
         <v>101345</v>
@@ -1465,17 +1448,16 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storheden, Dlr</t>
+          <t>Väst Storhedens skjutbana, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500210</v>
+        <v>500319</v>
       </c>
       <c r="R8" t="n">
-        <v>6729001</v>
+        <v>6729052</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1502,17 +1484,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-04-24</t>
+          <t>2013-06-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-04-24</t>
+          <t>2013-06-24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2 plantor, 2 blommor</t>
+          <t>I och på kanten av körväg. Sterila. Visades av förbipasserande med hund.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,31 +1503,35 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>I och i kant av sandig körväg</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Pär Dahlström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Pär Dahlström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84768990</t>
+          <t>https://artportalen.se/Sighting/6820542</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>84769049</v>
+        <v>84768990</v>
       </c>
       <c r="B9" t="n">
         <v>101345</v>
@@ -1592,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500291</v>
+        <v>500210</v>
       </c>
       <c r="R9" t="n">
-        <v>6729039</v>
+        <v>6729001</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1632,7 +1618,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2 plantor, inga knoppar/blommor</t>
+          <t>2 plantor, 2 blommor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,13 +1645,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84769049</t>
+          <t>https://artportalen.se/Sighting/84768990</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>84769057</v>
+        <v>84769049</v>
       </c>
       <c r="B10" t="n">
         <v>101345</v>
@@ -1695,7 +1681,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1712,10 +1698,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500317</v>
+        <v>500291</v>
       </c>
       <c r="R10" t="n">
-        <v>6729058</v>
+        <v>6729039</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1752,7 +1738,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>4 plantor, 1 blomma</t>
+          <t>2 plantor, inga knoppar/blommor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,13 +1765,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84769057</t>
+          <t>https://artportalen.se/Sighting/84769049</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117951359</v>
+        <v>84769057</v>
       </c>
       <c r="B11" t="n">
         <v>101345</v>
@@ -1815,7 +1801,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1823,23 +1809,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storhedens skjutbana väst om, Dlr</t>
+          <t>Storheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500288</v>
+        <v>500317</v>
       </c>
       <c r="R11" t="n">
-        <v>6729041</v>
+        <v>6729058</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1866,17 +1848,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2020-04-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2020-04-24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2 st varav 1 blommat samt en ca 8 m åt väster på samma höjd.</t>
+          <t>4 plantor, 1 blomma</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,74 +1871,84 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>åssida</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Pär Dahlström</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Pär Dahlström</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117951359</t>
+          <t>https://artportalen.se/Sighting/84769057</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110557603</v>
+        <v>117951359</v>
       </c>
       <c r="B12" t="n">
-        <v>91930</v>
+        <v>101345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>1853</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storhedens naturreservat, Storhedens naturreservat, Dlr</t>
+          <t>Storhedens skjutbana väst om, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500393</v>
+        <v>500288</v>
       </c>
       <c r="R12" t="n">
-        <v>6729112</v>
+        <v>6729041</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1980,22 +1972,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:43</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:43</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2 st varav 1 blommat samt en ca 8 m åt väster på samma höjd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2004,83 +1991,78 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>åssida</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Pär Dahlström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Pär Dahlström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110557603</t>
+          <t>https://artportalen.se/Sighting/117951359</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>84758529</v>
+        <v>110557603</v>
       </c>
       <c r="B13" t="n">
-        <v>57813</v>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100136</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storheden, Leksands kommun, Svealand, Storhedsvägen, Häradsbygden, Mjälgen,, Dlr</t>
+          <t>Storhedens naturreservat, Storhedens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500302</v>
+        <v>500393</v>
       </c>
       <c r="R13" t="n">
-        <v>6729006</v>
+        <v>6729112</v>
       </c>
       <c r="S13" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2104,27 +2086,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-04-24</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-04-24</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Flög söderut jagad av en trast</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2139,16 +2116,145 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110557603</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>84758529</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57813</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100136</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lappuggla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Strix nebulosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storheden, Leksands kommun, Svealand, Storhedsvägen, Häradsbygden, Mjälgen,, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>500302</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6729006</v>
+      </c>
+      <c r="S14" t="n">
+        <v>16</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-04-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-04-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Flög söderut jagad av en trast</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/84758529</t>
         </is>
@@ -2168,6 +2274,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 4464-2023 artfynd.xlsx
+++ b/artfynd/S 4464-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>136954306</v>
       </c>
       <c r="B4" t="n">
-        <v>43471</v>
+        <v>43484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 4464-2023 artfynd.xlsx
+++ b/artfynd/S 4464-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>136954306</v>
       </c>
       <c r="B4" t="n">
-        <v>43484</v>
+        <v>43486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 4464-2023 artfynd.xlsx
+++ b/artfynd/S 4464-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>136954306</v>
       </c>
       <c r="B4" t="n">
-        <v>43486</v>
+        <v>43496</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 4464-2023 artfynd.xlsx
+++ b/artfynd/S 4464-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>136954306</v>
       </c>
       <c r="B4" t="n">
-        <v>43496</v>
+        <v>43497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
